--- a/StructureDefinition-dk-core-person-servicerequest.xlsx
+++ b/StructureDefinition-dk-core-person-servicerequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T06:07:37+00:00</t>
+    <t>2024-10-27T12:31:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-person-servicerequest.xlsx
+++ b/StructureDefinition-dk-core-person-servicerequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-27T12:31:37+00:00</t>
+    <t>2024-11-04T14:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-person-servicerequest.xlsx
+++ b/StructureDefinition-dk-core-person-servicerequest.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:15:57+00:00</t>
+    <t>2024-11-04T14:58:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-person-servicerequest.xlsx
+++ b/StructureDefinition-dk-core-person-servicerequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T14:58:42+00:00</t>
+    <t>2024-11-04T15:07:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-dk-core-person-servicerequest.xlsx
+++ b/StructureDefinition-dk-core-person-servicerequest.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-04T15:07:28+00:00</t>
+    <t>2024-11-05T12:45:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
